--- a/MCP_Tool_Test_Matrix.xlsx
+++ b/MCP_Tool_Test_Matrix.xlsx
@@ -11,13 +11,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tool Tests" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Multi Tool Tests" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model Comparison" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run Log" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Direct MCP Proof" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run Log" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tool Tests'!$A$1:$L$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Multi Tool Tests'!$A$1:$H$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Model Comparison'!$A$1:$L$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Run Log'!$A$1:$Q$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Direct MCP Proof'!$A$1:$I$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Run Log'!$A$1:$Q$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -232,7 +234,25 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="RunLog" displayName="RunLog" ref="A1:Q31" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="DirectMcpProof" displayName="DirectMcpProof" ref="A1:I8" headerRowCount="1">
+  <autoFilter ref="A1:I8"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="Proof case"/>
+    <tableColumn id="2" name="MCP method/tool"/>
+    <tableColumn id="3" name="Payload template"/>
+    <tableColumn id="4" name="Evidence to capture"/>
+    <tableColumn id="5" name="Status"/>
+    <tableColumn id="6" name="Accepted?"/>
+    <tableColumn id="7" name="Rows/data?"/>
+    <tableColumn id="8" name="Error/code"/>
+    <tableColumn id="9" name="Notes / trace ID"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="RunLog" displayName="RunLog" ref="A1:Q31" headerRowCount="1">
   <autoFilter ref="A1:Q31"/>
   <tableColumns count="17">
     <tableColumn id="1" name="Date/time"/>
@@ -2118,6 +2138,312 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00087EA4"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="82" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Proof case</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>MCP method/tool</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Payload template</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Evidence to capture</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Accepted?</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Rows/data?</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Error/code</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Notes / trace ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="54" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>List available MCP tools</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>tools/list</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Confirms whether the deployed DaxView MCP exposes all expected tools, including voltage/current-capable telemetry.</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3" ht="54" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Direct site metadata</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>site_metadata_summary</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>{"authorization_id":"&lt;auth&gt;","site_id":&lt;site_id&gt;}</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Proves read access and site scope before testing historical metrics.</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="54" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Direct demand peak</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>demand_peak_summary</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>{"authorization_id":"&lt;auth&gt;","site_id":&lt;site_id&gt;,"start_time":"&lt;iso&gt;","end_time":"&lt;iso&gt;","timezone":"Asia/Kuala_Lumpur"}</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>If this returns NO_DATA, test the telemetry fallback below.</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Manual demand fallback source</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>telemetry_timeseries</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>{"authorization_id":"&lt;auth&gt;","site_id":&lt;site_id&gt;,"metric":"demand","start_time":"&lt;iso&gt;","end_time":"&lt;iso&gt;","bucket":"1h","aggregation":"auto","limit":1000}</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Use max(value/demand_kw/kw) from returned rows as fallback evidence.</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Voltage availability</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>telemetry_timeseries</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>{"authorization_id":"&lt;auth&gt;","device_id":&lt;device_id&gt;,"metric":"voltage","start_time":"&lt;iso&gt;","end_time":"&lt;iso&gt;","bucket":"1h","aggregation":"auto","limit":500}</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Records whether voltage is accepted and whether rows contain voltage values.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Current availability</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>telemetry_timeseries</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>{"authorization_id":"&lt;auth&gt;","device_id":&lt;device_id&gt;,"metric":"current","start_time":"&lt;iso&gt;","end_time":"&lt;iso&gt;","bucket":"1h","aggregation":"auto","limit":500}</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Records whether current is accepted and whether rows contain current values.</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Metric coverage check</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>data_availability_summary</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>{"authorization_id":"&lt;auth&gt;","site_id":&lt;site_id&gt;,"metric":"voltage","start_time":"&lt;iso&gt;","end_time":"&lt;iso&gt;","timezone":"Asia/Kuala_Lumpur"}</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>If supported, proves missing voltage data separately from unsupported telemetry.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I8"/>
+  <dataValidations count="3">
+    <dataValidation sqref="E2:E300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Not tested,Pass,Fail,Blocked,Tool unavailable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No,Partial,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="0016A34A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
